--- a/Papers/cohort_tracking.xlsx
+++ b/Papers/cohort_tracking.xlsx
@@ -1825,7 +1825,6 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
@@ -1988,7 +1987,6 @@
         </is>
       </c>
     </row>
-    <row r="89"/>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
@@ -2183,21 +2181,12 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr"/>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-    </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
           <t>OVERLAP TYPES (for Cohort Linkage)</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -2215,7 +2204,6 @@
           <t>Recommended Action</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2330,7 +2318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2534,6 +2522,2282 @@
       <c r="R2" s="2" t="inlineStr">
         <is>
           <t>HOPE ECD-DBD trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Hefler_2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Joshua Hefler</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Long-term outcomes after normothermic machine perf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>American Journal of Transplantation</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10.1016/j.ajt.2023.04.013</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Prospective cohort</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>University of Alberta Hospital</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2015-01-01/2021-12-31</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>NCT03089840</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>158</v>
+      </c>
+      <c r="O3" t="n">
+        <v>79</v>
+      </c>
+      <c r="P3" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>vanRijn_2021</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R. van Rijn</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Hypothermic Machine Perfusion in Liver Transplanta</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>New England Journal of Medicine</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10.1056/NEJMoa2031532</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>University Medical Center Groningen, Erasmus University Medical Center, Leiden University Medical Center, University Hospitals of Leuven, Ghent University Hospital, Kings College Hospital NHS Foundation Trust</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Netherlands,Belgium,United Kingdom</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2016-01/2019-07</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>NCT02584283</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>156</v>
+      </c>
+      <c r="O4" t="n">
+        <v>78</v>
+      </c>
+      <c r="P4" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jassem_2019</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Wayel Jassem</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10.1002/hep.30475</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>King's College Hospital, London</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2013-01/2013-12</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>14355416</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>39</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ghinolfi_2019</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Davide Ghinolfi</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Pilot, Open, Randomized, Prospective Trial for Nor</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Liver Transplantation</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10.1002/lt.25362</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>University of Pisa Medical School Hospital</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2016-09/2017-04</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>NCT02940600</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rayar_2021</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Michel Rayar</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Hypothermic oxygenated perfusion(HOPE) improves EC</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Liver Transplantation</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10.1002/lt.25955</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Prospective cohort</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CHU Rennes</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2010-01/2018-11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>NCT03376074</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>94</v>
+      </c>
+      <c r="O7" t="n">
+        <v>25</v>
+      </c>
+      <c r="P7" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Schlegel_2019</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Andrea Schlegel</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Journal of Hepatology</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10.1016/j.jhep.2018.10.005</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>University Hospital Zurich, Queen Elizabeth Hospital Birmingham</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Switzerland,United Kingdom</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2012-01/2017-03</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>100</v>
+      </c>
+      <c r="O8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P8" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mergental_2020</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hynek Mergental</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Transplantation of discarded livers following viab</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Nature Communications</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-020-16251-3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Prospective cohort</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Queen Elizabeth Hospital Birmingham</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2016-11/2018-02</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>NCT02740608</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>66</v>
+      </c>
+      <c r="O9" t="n">
+        <v>22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Nasralla_2018</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>David Nasralla</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A randomized trial of normothermic preservation in</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10.1038/s41586-018-0047-9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Addenbrooke’s Hospital, Cambridge, King’s College Hospital, London, Queen Elizabeth Hospital, Birmingham, Royal Free Hospital, London, Universitaire Ziekenhuizen, Leuven, Hospital Clínic de Barcelona, Universitatsklinikum, Essen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>UK,Belgium,Spain,Germany</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2014-06-26/2016-03-08</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ISRCTN 39731134</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>222</v>
+      </c>
+      <c r="O10" t="n">
+        <v>121</v>
+      </c>
+      <c r="P10" t="n">
+        <v>101</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Patrono_2019</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Damiano Patrono</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hypothermic Oxygenated Machine Perfusion of Liver </t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-019-45843-3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>A.O.U. Città della Salute e della Scienza di Torino</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Italy,Turin</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2016-03-16/2018-06-12</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>75</v>
+      </c>
+      <c r="O11" t="n">
+        <v>25</v>
+      </c>
+      <c r="P11" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ravaioli_2020</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Matteo Ravaioli</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Hypothermic Oxygenated New Machine Perfusion Syste</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Scientific Reports</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10.1038/s41598-020-62979-9</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>University of Bologna Sant’Orsola - Malpighi Hospital</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2016-10/2017-12</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>NCT03031067</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>40</v>
+      </c>
+      <c r="O12" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fodor_2021</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fodor</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Static cold storage compared with normothermic mac</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BJS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10.1093/bjs/znab118</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Medical University of Innsbruck</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2007-01/2020-04</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>118</v>
+      </c>
+      <c r="O13" t="n">
+        <v>59</v>
+      </c>
+      <c r="P13" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Panayotova_2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Panayotova</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portable hypothermic oxygenated machine perfusion </t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Hepatology</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10.1097/HEP.0000000000000715</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Rutgers New Jersey Medical School, Columbia University Medical Center, Intermountain Medical Center, Montefiore Medical Center, Northwestern Memorial Hospital, University of Chicago Medical Center, University of Cincinnati Medical Center, University of Rochester-Strong Memorial, University of Virginia Hospital</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2019-04/2021-07</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>NCT03484455</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>136</v>
+      </c>
+      <c r="O14" t="n">
+        <v>63</v>
+      </c>
+      <c r="P14" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dutkowski_2015</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dutkowski</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2015</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>First Comparison of Hypothermic Oxygenated PErfusi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000001473</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>University Hospital Zurich, Erasmus Medical Centre Rotterdam, Queen Elizabeth Hospital Birmingham</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Switzerland,Netherlands,United Kingdom</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2005-01/2014-12</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>75</v>
+      </c>
+      <c r="O15" t="n">
+        <v>25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Czigany_2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Zoltan Czigany</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hypothermic Oxygenated Machine Perfusion Reduces E</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000005110</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>University Hospital RWTH Aachen, Aachen, Germany, Charite-Universitatsmedizin Berlin, Berlin, Germany, Ludwig-Maximilians-University Munich, Munich, Germany, Institute for Clinical and Experimental Medicine, Prague, Czech Republic</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Germany,Czech Republic</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2017-09/2020-09</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>NCT03124641</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>46</v>
+      </c>
+      <c r="O16" t="n">
+        <v>23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gaurav_2022</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rohit Gaurav</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Liver Transplantation Outcomes From Controlled Cir</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000005428</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Addenbrooke’s Hospital, Cambridge</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2013-01/2020-10</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>233</v>
+      </c>
+      <c r="O17" t="n">
+        <v>67</v>
+      </c>
+      <c r="P17" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chapman_2023</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>William C. Chapman</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Normothermic Machine Perfusion of Donor Livers for</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000005934</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Washington University, St. Louis, Duke University, University of Wisconsin, Madison, University of Miami, Indiana University, University of Pennsylvania, University of Michigan, University of Chicago, University of Maryland, UCLA, Beth Israel Deaconess Medical Center, University of Alabama, USC, Mayo Clinic, Arizona, UCSF, Ochsner Clinic, Tampa General Hospital</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2016-10/2020-02</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>NCT02478151</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>383</v>
+      </c>
+      <c r="O18" t="n">
+        <v>136</v>
+      </c>
+      <c r="P18" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Grat_2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Michał Grąt</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Routine End-ischemic Hypothermic Oxygenated Machin</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000006055</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Department of General, Transplant and Liver Surgery, Medical University of Warsaw</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2021-04/2022-05</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>NCT04812054</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>104</v>
+      </c>
+      <c r="O19" t="n">
+        <v>26</v>
+      </c>
+      <c r="P19" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Wehrle_2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chase J. Wehrle</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Impact of Back-to-Base Normothermic Machine Perfus</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000006291</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Cleveland Clinic, Cleveland, OH, Cleveland Clinic Florida, Weston, FL</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2019-01/2023-09</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>111</v>
+      </c>
+      <c r="O20" t="n">
+        <v>37</v>
+      </c>
+      <c r="P20" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bral_2017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M. Bral</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2017</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Preliminary Single-Center Canadian Experience of H</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>American Journal of Transplantation</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10.1111/ajt.14049</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>University of Alberta Hospital, Edmonton</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2015-02/2015-12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Pro00043239</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>36</v>
+      </c>
+      <c r="O21" t="n">
+        <v>9</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ravaioli_2022</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Matteo Ravaioli</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Hypothermic oxygenated perfusion in extended crite</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>American Journal of Transplantation</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10.1111/ajt.17115</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>IRCCS Azienda Ospedaliero-Universitaria di Bologna</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2018-12/2021-01</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>NCT03837197</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>110</v>
+      </c>
+      <c r="O22" t="n">
+        <v>55</v>
+      </c>
+      <c r="P22" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Norén_2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Norén</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>End-ischemic hypothermic oxygenated machine perfus</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Artificial Organs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10.1111/aor.14640</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sahlgrenska University Hospital</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2017-01/2022-12</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>77</v>
+      </c>
+      <c r="O23" t="n">
+        <v>30</v>
+      </c>
+      <c r="P23" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Lesurtel_2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Mickaël Lesurtel</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A French multicenter randomized controlled trial o</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>American Journal of Transplantation</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10.1016/j.ajt.2025.10.006</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Beaujon Hospital, Clichy, Croix Rousse University Hospital, Lyon, Paul Brousse University Hospital, Villejuif, Pontchaillou University Hospital, Rennes, Claude Huriez University Hospital, Lille, Pitié-Salpêtrière Hospital, Paris, Grenoble Alpes University Hospital, Grenoble, Hautepierre Hospital, Strasbourg</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2019-09/2023-03</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>NCT03929523</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>262</v>
+      </c>
+      <c r="O24" t="n">
+        <v>131</v>
+      </c>
+      <c r="P24" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Shu_2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wenzhi Shu</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine perfusion prevents early tumor recurrence </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Cancer Letters</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10.1016/j.canlet.2025.217970</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>United Network for Organ Sharing (UNOS) database (Multicenter)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2015-04/2024-01</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>822</v>
+      </c>
+      <c r="O25" t="n">
+        <v>411</v>
+      </c>
+      <c r="P25" t="n">
+        <v>411</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Mixed (HMP/NMP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Coquelle_2025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Agathe Coquelle</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Long-term outcomes of hypothermic oxygenated machi</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>BJS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10.1093/bjs/znaf202</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Hôpital Pontchaillou, Université Rennes 1, Rennes</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2018-01/2021-11</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>PERPHO study (Rayar et al. 2021)</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>138</v>
+      </c>
+      <c r="O26" t="n">
+        <v>49</v>
+      </c>
+      <c r="P26" t="n">
+        <v>89</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Czigany_2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Zoltan Czigany</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Improved outcomes after hypothermic oxygenated mac</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hepatology Communications</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10.1097/HC9.0000000000000376</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Department of Surgery, Campus Charité Mitte | Campus Virchow-Klinikum, Charité – Universitätsmedizin Berlin, Germany, Department of Surgery and Transplantation, University Hospital RWTH Aachen, Germany, Department of Transplantation Surgery, Institute for Clinical and Experimental Medicine, Prague, Czech Republic, Department of General Surgery and Liver Transplantation, Fundeni Clinical Institute, Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Germany,Czech Republic,Romania</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2017-09/2020-09</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>NCT03124641</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>46</v>
+      </c>
+      <c r="O27" t="n">
+        <v>23</v>
+      </c>
+      <c r="P27" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Morawski_2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Marcin Morawski</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Routine end-ischemic hypothermic machine perfusion</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>International Journal of Surgery</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10.1097/JS9.0000000000001919</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Department of General, Transplant, and Liver Surgery, Medical University of Warsaw</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2021-04/2022-05</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>NCT04812054</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>40</v>
+      </c>
+      <c r="O28" t="n">
+        <v>14</v>
+      </c>
+      <c r="P28" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Okumura_2024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Kenji Okumura</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normothermic Machine Perfusion Is Associated With </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Transplantation Direct</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10.1097/TXD.0000000000001679</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>UNOS (United Network for Organ Sharing) - Nationwide US database</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2016-01/2022-12</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>496</v>
+      </c>
+      <c r="O29" t="n">
+        <v>248</v>
+      </c>
+      <c r="P29" t="n">
+        <v>248</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Wang_2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Benjamin K Wang</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>From Patients to Providers: Assessing Impact of No</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Journal of the American College of Surgeons</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>10.1097/XCS.0000000000000924</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>All US transplant centers reporting to UNOS</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2016-01-01/2022-12-31</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>919</v>
+      </c>
+      <c r="O30" t="n">
+        <v>462</v>
+      </c>
+      <c r="P30" t="n">
+        <v>457</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>NMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Elgosbi_2025</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Marwa Elgosbi</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hypothermic oxygenated machine perfusion influence</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Liver Transplantation</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10.1097/LVT.0000000000000461</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>King’s College Hospital, London</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2018-11/2019-07</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>NCT02520739, NCT03124641</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>27</v>
+      </c>
+      <c r="O31" t="n">
+        <v>14</v>
+      </c>
+      <c r="P31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>vanRijn_2025</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rianne van Rijn</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Long-term Follow-up After Hypothermic Oxygenated M</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>NCT02584283</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>University Medical Center Groningen, Erasmus MC Rotterdam, KU Leuven, Ghent University Hospital, Leiden University Medical Center, King's College Hospital London</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Netherlands,Belgium,United Kingdom</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2016-01/2019-07</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>NCT02584283</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>156</v>
+      </c>
+      <c r="O32" t="n">
+        <v>78</v>
+      </c>
+      <c r="P32" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Eden_2025</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Janina Eden</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Life Expectancy of Transplanted Livers: HOPE Again</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Annals of Surgery</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10.1097/SLA.0000000000006883</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>University Hospital Zurich, 22 European centers (HOPE-REAL)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Netherlands,Switzerland,Austria,Germany,Romania,Italy,Portugal,Czech Republic,Belgium,France,Sweden</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>1986-01/2022-12</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>NCT05520320</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>836</v>
+      </c>
+      <c r="O33" t="n">
+        <v>432</v>
+      </c>
+      <c r="P33" t="n">
+        <v>404</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Endo_2025</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Endo</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cost-effectiveness of Dual Hypothermic Oxygenated </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Transplantation</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10.1097/TP.0000000000005232</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>RCT</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Erasmus MC Transplant Institute, Rotterdam, University Medical Center Groningen, Leiden University Medical Center</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NCT02584283</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>119</v>
+      </c>
+      <c r="O34" t="n">
+        <v>60</v>
+      </c>
+      <c r="P34" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DeStefano_2025</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nicola De Stefano</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Advanced Perfusion Techniques Level Liver Transpla</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Transplantation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10.1097/TP.0000000000005545</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Azienda Ospedaliero Universitaria Città della Salute e della Scienza di Torino</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2016-01/2024-06</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NCT04744389</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>305</v>
+      </c>
+      <c r="O35" t="n">
+        <v>122</v>
+      </c>
+      <c r="P35" t="n">
+        <v>122</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>HOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Corcione_2025</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Silvia Corcione</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hypothermic oxygenated machine perfusion does not </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>HepatoBiliary Surg Nutr</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10.21037/hbsn-24-552</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Retrospective cohort</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Azienda Ospedaliero Universitaria (AOU) City of Health and Sciences of Turin (Molinette Hospital)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2016-03/2023-06</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>370</v>
+      </c>
+      <c r="O36" t="n">
+        <v>185</v>
+      </c>
+      <c r="P36" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>HOPE</t>
         </is>
       </c>
     </row>
